--- a/output-app/AUDIT_TRAIL.xlsx
+++ b/output-app/AUDIT_TRAIL.xlsx
@@ -406,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G23"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -459,7 +459,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Tanggal Cetak: 24/7/2026, 15.02.53</v>
+        <v>Tanggal Cetak: 25/7/2026, 18.00.19</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -525,22 +525,22 @@
         <v>1</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-07-24 03:30:09</v>
+        <v>2026-07-25 10:38:59</v>
       </c>
       <c r="C6" t="str">
-        <v>TRANSAKSI</v>
+        <v>AKSESORIES.xls</v>
       </c>
       <c r="D6" t="str">
-        <v>Sistem Keuangan</v>
+        <v>AKSESORIES.xls</v>
       </c>
       <c r="E6" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
+        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
       </c>
       <c r="F6" t="str">
         <v>BALANCED</v>
       </c>
       <c r="G6" t="str">
-        <v>Total Debit: Rp 79.000 | Total Kredit: Rp 79.000</v>
+        <v>Total Debit: Rp 21.696.230.000,277 | Total Kredit: Rp 21.696.230.000,277</v>
       </c>
     </row>
     <row r="7">
@@ -548,22 +548,22 @@
         <v>2</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-07-24 03:30:09</v>
+        <v>2026-07-25 10:39:00</v>
       </c>
       <c r="C7" t="str">
-        <v>TRANSAKSI</v>
+        <v>Daftar Voucher.xlsx</v>
       </c>
       <c r="D7" t="str">
-        <v>Sistem Keuangan</v>
+        <v>Daftar Voucher.xlsx</v>
       </c>
       <c r="E7" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
       </c>
       <c r="F7" t="str">
         <v>BALANCED</v>
       </c>
       <c r="G7" t="str">
-        <v>Total Debit: Rp 361.700 | Total Kredit: Rp 361.700</v>
+        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
       </c>
     </row>
     <row r="8">
@@ -571,22 +571,22 @@
         <v>3</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-07-24 03:30:09</v>
+        <v>2026-07-25 10:39:00</v>
       </c>
       <c r="C8" t="str">
-        <v>TRANSAKSI</v>
+        <v>Daftar Voucher.xlsx</v>
       </c>
       <c r="D8" t="str">
-        <v>Sistem Keuangan</v>
+        <v>Daftar Voucher.xlsx</v>
       </c>
       <c r="E8" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
       </c>
       <c r="F8" t="str">
         <v>BALANCED</v>
       </c>
       <c r="G8" t="str">
-        <v>Total Debit: Rp 302.900 | Total Kredit: Rp 302.900</v>
+        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
       </c>
     </row>
     <row r="9">
@@ -594,22 +594,22 @@
         <v>4</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-07-24 03:30:12</v>
+        <v>2026-07-25 10:39:00</v>
       </c>
       <c r="C9" t="str">
-        <v>TRANSAKSI</v>
+        <v>Jurnal Bayar.xlsx</v>
       </c>
       <c r="D9" t="str">
-        <v>Sistem Keuangan</v>
+        <v>Jurnal Bayar.xlsx</v>
       </c>
       <c r="E9" t="str">
-        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
+        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
       </c>
       <c r="F9" t="str">
         <v>BALANCED</v>
       </c>
       <c r="G9" t="str">
-        <v>Total Debit: Rp 21.696.230.000,277 | Total Kredit: Rp 21.696.230.000,277</v>
+        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
       </c>
     </row>
     <row r="10">
@@ -617,22 +617,22 @@
         <v>5</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-07-24 03:30:12</v>
+        <v>2026-07-25 10:39:00</v>
       </c>
       <c r="C10" t="str">
-        <v>TRANSAKSI</v>
+        <v>Jurnal Bayar.xlsx</v>
       </c>
       <c r="D10" t="str">
-        <v>Sistem Keuangan</v>
+        <v>Jurnal Bayar.xlsx</v>
       </c>
       <c r="E10" t="str">
-        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
       </c>
       <c r="F10" t="str">
         <v>BALANCED</v>
       </c>
       <c r="G10" t="str">
-        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
+        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
       </c>
     </row>
     <row r="11">
@@ -640,22 +640,22 @@
         <v>6</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-07-24 03:30:12</v>
+        <v>2026-07-25 10:39:00</v>
       </c>
       <c r="C11" t="str">
-        <v>TRANSAKSI</v>
+        <v>Persediaan Bahan Kimia &amp; BBM.xlsx</v>
       </c>
       <c r="D11" t="str">
-        <v>Sistem Keuangan</v>
+        <v>Persediaan Bahan Kimia &amp; BBM.xlsx</v>
       </c>
       <c r="E11" t="str">
-        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+        <v>Persediaan Bahan Kimia &amp; BBM</v>
       </c>
       <c r="F11" t="str">
         <v>BALANCED</v>
       </c>
       <c r="G11" t="str">
-        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
+        <v>Total Debit: Rp 644 | Total Kredit: Rp 644</v>
       </c>
     </row>
     <row r="12">
@@ -663,22 +663,22 @@
         <v>7</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-07-24 03:30:13</v>
+        <v>2026-07-25 10:39:01</v>
       </c>
       <c r="C12" t="str">
-        <v>TRANSAKSI</v>
+        <v>LPP tgl 18 mei (koperasi).xls</v>
       </c>
       <c r="D12" t="str">
-        <v>Sistem Keuangan</v>
+        <v>LPP tgl 18 mei (koperasi).xls</v>
       </c>
       <c r="E12" t="str">
-        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+        <v>Penerimaan Rek Air (KOPERASI)</v>
       </c>
       <c r="F12" t="str">
         <v>BALANCED</v>
       </c>
       <c r="G12" t="str">
-        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
+        <v>Total Debit: Rp 79.000 | Total Kredit: Rp 79.000</v>
       </c>
     </row>
     <row r="13">
@@ -686,22 +686,22 @@
         <v>8</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-07-24 03:30:13</v>
+        <v>2026-07-25 10:39:01</v>
       </c>
       <c r="C13" t="str">
-        <v>TRANSAKSI</v>
+        <v>LPP tgl 18 mei (loket cabang).xls</v>
       </c>
       <c r="D13" t="str">
-        <v>Sistem Keuangan</v>
+        <v>LPP tgl 18 mei (loket cabang).xls</v>
       </c>
       <c r="E13" t="str">
-        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
       </c>
       <c r="F13" t="str">
         <v>BALANCED</v>
       </c>
       <c r="G13" t="str">
-        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
+        <v>Total Debit: Rp 361.700 | Total Kredit: Rp 361.700</v>
       </c>
     </row>
     <row r="14">
@@ -709,22 +709,22 @@
         <v>9</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-07-24 03:30:13</v>
+        <v>2026-07-25 10:39:01</v>
       </c>
       <c r="C14" t="str">
-        <v>TRANSAKSI</v>
+        <v>LPP tgl 18 mei (loket kantor).xls</v>
       </c>
       <c r="D14" t="str">
-        <v>Sistem Keuangan</v>
+        <v>LPP tgl 18 mei (loket kantor).xls</v>
       </c>
       <c r="E14" t="str">
-        <v>Persediaan Bahan Kimia &amp; BBM</v>
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
       </c>
       <c r="F14" t="str">
         <v>BALANCED</v>
       </c>
       <c r="G14" t="str">
-        <v>Total Debit: Rp 644 | Total Kredit: Rp 644</v>
+        <v>Total Debit: Rp 302.900 | Total Kredit: Rp 302.900</v>
       </c>
     </row>
     <row r="15">
@@ -732,22 +732,22 @@
         <v>10</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-07-24 03:41:13</v>
+        <v>2026-07-25 11:00:17</v>
       </c>
       <c r="C15" t="str">
-        <v>TRANSAKSI</v>
+        <v>AKSESORIES.xls</v>
       </c>
       <c r="D15" t="str">
-        <v>Sistem Keuangan</v>
+        <v>AKSESORIES.xls</v>
       </c>
       <c r="E15" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
+        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
       </c>
       <c r="F15" t="str">
         <v>BALANCED</v>
       </c>
       <c r="G15" t="str">
-        <v>Total Debit: Rp 79.000 | Total Kredit: Rp 79.000</v>
+        <v>Total Debit: Rp 21.696.230.000,277 | Total Kredit: Rp 21.696.230.000,277</v>
       </c>
     </row>
     <row r="16">
@@ -755,22 +755,22 @@
         <v>11</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-07-24 03:41:13</v>
+        <v>2026-07-25 11:00:18</v>
       </c>
       <c r="C16" t="str">
-        <v>TRANSAKSI</v>
+        <v>Daftar Voucher.xlsx</v>
       </c>
       <c r="D16" t="str">
-        <v>Sistem Keuangan</v>
+        <v>Daftar Voucher.xlsx</v>
       </c>
       <c r="E16" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
       </c>
       <c r="F16" t="str">
         <v>BALANCED</v>
       </c>
       <c r="G16" t="str">
-        <v>Total Debit: Rp 361.700 | Total Kredit: Rp 361.700</v>
+        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
       </c>
     </row>
     <row r="17">
@@ -778,22 +778,22 @@
         <v>12</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-07-24 03:41:13</v>
+        <v>2026-07-25 11:00:18</v>
       </c>
       <c r="C17" t="str">
-        <v>TRANSAKSI</v>
+        <v>Daftar Voucher.xlsx</v>
       </c>
       <c r="D17" t="str">
-        <v>Sistem Keuangan</v>
+        <v>Daftar Voucher.xlsx</v>
       </c>
       <c r="E17" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
       </c>
       <c r="F17" t="str">
         <v>BALANCED</v>
       </c>
       <c r="G17" t="str">
-        <v>Total Debit: Rp 302.900 | Total Kredit: Rp 302.900</v>
+        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
       </c>
     </row>
     <row r="18">
@@ -801,22 +801,22 @@
         <v>13</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-07-24 03:42:42</v>
+        <v>2026-07-25 11:00:18</v>
       </c>
       <c r="C18" t="str">
-        <v>TRANSAKSI</v>
+        <v>Jurnal Bayar.xlsx</v>
       </c>
       <c r="D18" t="str">
-        <v>Sistem Keuangan</v>
+        <v>Jurnal Bayar.xlsx</v>
       </c>
       <c r="E18" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
+        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
       </c>
       <c r="F18" t="str">
         <v>BALANCED</v>
       </c>
       <c r="G18" t="str">
-        <v>Total Debit: Rp 79.000 | Total Kredit: Rp 79.000</v>
+        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
       </c>
     </row>
     <row r="19">
@@ -824,22 +824,22 @@
         <v>14</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-07-24 03:42:43</v>
+        <v>2026-07-25 11:00:18</v>
       </c>
       <c r="C19" t="str">
-        <v>TRANSAKSI</v>
+        <v>Jurnal Bayar.xlsx</v>
       </c>
       <c r="D19" t="str">
-        <v>Sistem Keuangan</v>
+        <v>Jurnal Bayar.xlsx</v>
       </c>
       <c r="E19" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
       </c>
       <c r="F19" t="str">
         <v>BALANCED</v>
       </c>
       <c r="G19" t="str">
-        <v>Total Debit: Rp 361.700 | Total Kredit: Rp 361.700</v>
+        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
       </c>
     </row>
     <row r="20">
@@ -847,22 +847,22 @@
         <v>15</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-07-24 03:42:43</v>
+        <v>2026-07-25 11:00:18</v>
       </c>
       <c r="C20" t="str">
-        <v>TRANSAKSI</v>
+        <v>Persediaan Bahan Kimia &amp; BBM.xlsx</v>
       </c>
       <c r="D20" t="str">
-        <v>Sistem Keuangan</v>
+        <v>Persediaan Bahan Kimia &amp; BBM.xlsx</v>
       </c>
       <c r="E20" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+        <v>Persediaan Bahan Kimia &amp; BBM</v>
       </c>
       <c r="F20" t="str">
         <v>BALANCED</v>
       </c>
       <c r="G20" t="str">
-        <v>Total Debit: Rp 302.900 | Total Kredit: Rp 302.900</v>
+        <v>Total Debit: Rp 644 | Total Kredit: Rp 644</v>
       </c>
     </row>
     <row r="21">
@@ -870,13 +870,13 @@
         <v>16</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-07-24 06:36:16</v>
+        <v>2026-07-25 11:00:18</v>
       </c>
       <c r="C21" t="str">
-        <v>TRANSAKSI</v>
+        <v>LPP tgl 18 mei (koperasi).xls</v>
       </c>
       <c r="D21" t="str">
-        <v>Sistem Keuangan</v>
+        <v>LPP tgl 18 mei (koperasi).xls</v>
       </c>
       <c r="E21" t="str">
         <v>Penerimaan Rek Air (KOPERASI)</v>
@@ -893,13 +893,13 @@
         <v>17</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-07-24 06:36:16</v>
+        <v>2026-07-25 11:00:18</v>
       </c>
       <c r="C22" t="str">
-        <v>TRANSAKSI</v>
+        <v>LPP tgl 18 mei (loket cabang).xls</v>
       </c>
       <c r="D22" t="str">
-        <v>Sistem Keuangan</v>
+        <v>LPP tgl 18 mei (loket cabang).xls</v>
       </c>
       <c r="E22" t="str">
         <v>Penerimaan Rek Air (LOKET CABANG)</v>
@@ -916,13 +916,13 @@
         <v>18</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-07-24 06:36:16</v>
+        <v>2026-07-25 11:00:18</v>
       </c>
       <c r="C23" t="str">
-        <v>TRANSAKSI</v>
+        <v>LPP tgl 18 mei (loket kantor).xls</v>
       </c>
       <c r="D23" t="str">
-        <v>Sistem Keuangan</v>
+        <v>LPP tgl 18 mei (loket kantor).xls</v>
       </c>
       <c r="E23" t="str">
         <v>Penerimaan Rek Air (LOKET KANTOR)</v>
@@ -934,676 +934,9 @@
         <v>Total Debit: Rp 302.900 | Total Kredit: Rp 302.900</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24">
-        <v>19</v>
-      </c>
-      <c r="B24" t="str">
-        <v>2026-07-24 07:01:01</v>
-      </c>
-      <c r="C24" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E24" t="str">
-        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
-      </c>
-      <c r="F24" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Total Debit: Rp 21.696.230.000,277 | Total Kredit: Rp 21.696.230.000,277</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>20</v>
-      </c>
-      <c r="B25" t="str">
-        <v>2026-07-24 07:01:02</v>
-      </c>
-      <c r="C25" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E25" t="str">
-        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
-      </c>
-      <c r="F25" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>21</v>
-      </c>
-      <c r="B26" t="str">
-        <v>2026-07-24 07:01:02</v>
-      </c>
-      <c r="C26" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E26" t="str">
-        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
-      </c>
-      <c r="F26" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>22</v>
-      </c>
-      <c r="B27" t="str">
-        <v>2026-07-24 07:01:02</v>
-      </c>
-      <c r="C27" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E27" t="str">
-        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
-      </c>
-      <c r="F27" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G27" t="str">
-        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>23</v>
-      </c>
-      <c r="B28" t="str">
-        <v>2026-07-24 07:01:02</v>
-      </c>
-      <c r="C28" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E28" t="str">
-        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
-      </c>
-      <c r="F28" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G28" t="str">
-        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>24</v>
-      </c>
-      <c r="B29" t="str">
-        <v>2026-07-24 07:01:03</v>
-      </c>
-      <c r="C29" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E29" t="str">
-        <v>Persediaan Bahan Kimia &amp; BBM</v>
-      </c>
-      <c r="F29" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G29" t="str">
-        <v>Total Debit: Rp 644 | Total Kredit: Rp 644</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>25</v>
-      </c>
-      <c r="B30" t="str">
-        <v>2026-07-24 07:01:04</v>
-      </c>
-      <c r="C30" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E30" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
-      </c>
-      <c r="F30" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G30" t="str">
-        <v>Total Debit: Rp 79.000 | Total Kredit: Rp 79.000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>26</v>
-      </c>
-      <c r="B31" t="str">
-        <v>2026-07-24 07:01:04</v>
-      </c>
-      <c r="C31" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D31" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E31" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
-      </c>
-      <c r="F31" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G31" t="str">
-        <v>Total Debit: Rp 361.700 | Total Kredit: Rp 361.700</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>27</v>
-      </c>
-      <c r="B32" t="str">
-        <v>2026-07-24 07:01:04</v>
-      </c>
-      <c r="C32" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D32" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E32" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
-      </c>
-      <c r="F32" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G32" t="str">
-        <v>Total Debit: Rp 302.900 | Total Kredit: Rp 302.900</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>28</v>
-      </c>
-      <c r="B33" t="str">
-        <v>2026-07-24 07:02:05</v>
-      </c>
-      <c r="C33" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D33" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E33" t="str">
-        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
-      </c>
-      <c r="F33" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G33" t="str">
-        <v>Total Debit: Rp 21.696.230.000,277 | Total Kredit: Rp 21.696.230.000,277</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>29</v>
-      </c>
-      <c r="B34" t="str">
-        <v>2026-07-24 07:02:05</v>
-      </c>
-      <c r="C34" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D34" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E34" t="str">
-        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
-      </c>
-      <c r="F34" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G34" t="str">
-        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>30</v>
-      </c>
-      <c r="B35" t="str">
-        <v>2026-07-24 07:02:05</v>
-      </c>
-      <c r="C35" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D35" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E35" t="str">
-        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
-      </c>
-      <c r="F35" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G35" t="str">
-        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>31</v>
-      </c>
-      <c r="B36" t="str">
-        <v>2026-07-24 07:02:06</v>
-      </c>
-      <c r="C36" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D36" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E36" t="str">
-        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
-      </c>
-      <c r="F36" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G36" t="str">
-        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>32</v>
-      </c>
-      <c r="B37" t="str">
-        <v>2026-07-24 07:02:06</v>
-      </c>
-      <c r="C37" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D37" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E37" t="str">
-        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
-      </c>
-      <c r="F37" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G37" t="str">
-        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>33</v>
-      </c>
-      <c r="B38" t="str">
-        <v>2026-07-24 07:02:07</v>
-      </c>
-      <c r="C38" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D38" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E38" t="str">
-        <v>Persediaan Bahan Kimia &amp; BBM</v>
-      </c>
-      <c r="F38" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G38" t="str">
-        <v>Total Debit: Rp 644 | Total Kredit: Rp 644</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>34</v>
-      </c>
-      <c r="B39" t="str">
-        <v>2026-07-24 07:02:07</v>
-      </c>
-      <c r="C39" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D39" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E39" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
-      </c>
-      <c r="F39" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G39" t="str">
-        <v>Total Debit: Rp 79.000 | Total Kredit: Rp 79.000</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>35</v>
-      </c>
-      <c r="B40" t="str">
-        <v>2026-07-24 07:02:07</v>
-      </c>
-      <c r="C40" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D40" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E40" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
-      </c>
-      <c r="F40" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G40" t="str">
-        <v>Total Debit: Rp 361.700 | Total Kredit: Rp 361.700</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>36</v>
-      </c>
-      <c r="B41" t="str">
-        <v>2026-07-24 07:02:07</v>
-      </c>
-      <c r="C41" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D41" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E41" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
-      </c>
-      <c r="F41" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G41" t="str">
-        <v>Total Debit: Rp 302.900 | Total Kredit: Rp 302.900</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>37</v>
-      </c>
-      <c r="B42" t="str">
-        <v>2026-07-24 07:43:30</v>
-      </c>
-      <c r="C42" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D42" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E42" t="str">
-        <v>PEMBELIAN KAPORIT</v>
-      </c>
-      <c r="F42" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G42" t="str">
-        <v>Total Debit: Rp 100.000 | Total Kredit: Rp 100.000</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>38</v>
-      </c>
-      <c r="B43" t="str">
-        <v>2026-07-24 07:58:51</v>
-      </c>
-      <c r="C43" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D43" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E43" t="str">
-        <v>Tes Transaksi Terbaru Paling Atas</v>
-      </c>
-      <c r="F43" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G43" t="str">
-        <v>Total Debit: Rp 500.000 | Total Kredit: Rp 500.000</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>39</v>
-      </c>
-      <c r="B44" t="str">
-        <v>2026-07-24 08:02:51</v>
-      </c>
-      <c r="C44" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D44" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E44" t="str">
-        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
-      </c>
-      <c r="F44" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G44" t="str">
-        <v>Total Debit: Rp 21.696.230.000,277 | Total Kredit: Rp 21.696.230.000,277</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>40</v>
-      </c>
-      <c r="B45" t="str">
-        <v>2026-07-24 08:02:51</v>
-      </c>
-      <c r="C45" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D45" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E45" t="str">
-        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
-      </c>
-      <c r="F45" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G45" t="str">
-        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>41</v>
-      </c>
-      <c r="B46" t="str">
-        <v>2026-07-24 08:02:51</v>
-      </c>
-      <c r="C46" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D46" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E46" t="str">
-        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
-      </c>
-      <c r="F46" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G46" t="str">
-        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>42</v>
-      </c>
-      <c r="B47" t="str">
-        <v>2026-07-24 08:02:52</v>
-      </c>
-      <c r="C47" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D47" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E47" t="str">
-        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
-      </c>
-      <c r="F47" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G47" t="str">
-        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>43</v>
-      </c>
-      <c r="B48" t="str">
-        <v>2026-07-24 08:02:52</v>
-      </c>
-      <c r="C48" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D48" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E48" t="str">
-        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
-      </c>
-      <c r="F48" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G48" t="str">
-        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>44</v>
-      </c>
-      <c r="B49" t="str">
-        <v>2026-07-24 08:02:52</v>
-      </c>
-      <c r="C49" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D49" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E49" t="str">
-        <v>Persediaan Bahan Kimia &amp; BBM</v>
-      </c>
-      <c r="F49" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G49" t="str">
-        <v>Total Debit: Rp 644 | Total Kredit: Rp 644</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>45</v>
-      </c>
-      <c r="B50" t="str">
-        <v>2026-07-24 08:02:53</v>
-      </c>
-      <c r="C50" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D50" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E50" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
-      </c>
-      <c r="F50" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G50" t="str">
-        <v>Total Debit: Rp 79.000 | Total Kredit: Rp 79.000</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>46</v>
-      </c>
-      <c r="B51" t="str">
-        <v>2026-07-24 08:02:53</v>
-      </c>
-      <c r="C51" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D51" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E51" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
-      </c>
-      <c r="F51" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G51" t="str">
-        <v>Total Debit: Rp 361.700 | Total Kredit: Rp 361.700</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>47</v>
-      </c>
-      <c r="B52" t="str">
-        <v>2026-07-24 08:02:53</v>
-      </c>
-      <c r="C52" t="str">
-        <v>TRANSAKSI</v>
-      </c>
-      <c r="D52" t="str">
-        <v>Sistem Keuangan</v>
-      </c>
-      <c r="E52" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
-      </c>
-      <c r="F52" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G52" t="str">
-        <v>Total Debit: Rp 302.900 | Total Kredit: Rp 302.900</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output-app/AUDIT_TRAIL.xlsx
+++ b/output-app/AUDIT_TRAIL.xlsx
@@ -32,17 +32,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="10">
-    <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -406,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:K5"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -415,6 +406,10 @@
     <col min="5" max="5" width="45.83203125" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" customWidth="1"/>
     <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="65.83203125" customWidth="1"/>
+    <col min="9" max="9" width="65.83203125" customWidth="1"/>
+    <col min="10" max="10" width="100.83203125" customWidth="1"/>
+    <col min="11" max="11" width="100.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -436,10 +431,22 @@
       <c r="F1" t="str">
         <v/>
       </c>
+      <c r="G1" t="str">
+        <v/>
+      </c>
+      <c r="H1" t="str">
+        <v/>
+      </c>
+      <c r="I1" t="str">
+        <v/>
+      </c>
+      <c r="J1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AUDIT TRAIL &amp; LOG PEMROSESAN DATA KEUANGAN</v>
+        <v>AUDIT TRAIL (CRYPTOGRAPHIC LOG &amp; DATA SNAPSHOTS)</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -454,12 +461,24 @@
         <v/>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Tanggal Cetak: 25/7/2026, 18.00.19</v>
+        <v>Tanggal Cetak: 29/7/2026, 11.53.08</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -474,6 +493,18 @@
         <v/>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
         <v/>
       </c>
     </row>
@@ -494,6 +525,18 @@
         <v/>
       </c>
       <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
         <v/>
       </c>
     </row>
@@ -519,424 +562,22 @@
       <c r="G5" t="str">
         <v>Detail Mutasi / Ringkasan</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-07-25 10:38:59</v>
-      </c>
-      <c r="C6" t="str">
-        <v>AKSESORIES.xls</v>
-      </c>
-      <c r="D6" t="str">
-        <v>AKSESORIES.xls</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
-      </c>
-      <c r="F6" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Total Debit: Rp 21.696.230.000,277 | Total Kredit: Rp 21.696.230.000,277</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-07-25 10:39:00</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Daftar Voucher.xlsx</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Daftar Voucher.xlsx</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
-      </c>
-      <c r="F7" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-07-25 10:39:00</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Daftar Voucher.xlsx</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Daftar Voucher.xlsx</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
-      </c>
-      <c r="F8" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>4</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-07-25 10:39:00</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Jurnal Bayar.xlsx</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Jurnal Bayar.xlsx</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
-      </c>
-      <c r="F9" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>5</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-07-25 10:39:00</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Jurnal Bayar.xlsx</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Jurnal Bayar.xlsx</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
-      </c>
-      <c r="F10" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>6</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-07-25 10:39:00</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Persediaan Bahan Kimia &amp; BBM.xlsx</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Persediaan Bahan Kimia &amp; BBM.xlsx</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Persediaan Bahan Kimia &amp; BBM</v>
-      </c>
-      <c r="F11" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Total Debit: Rp 644 | Total Kredit: Rp 644</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>7</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-07-25 10:39:01</v>
-      </c>
-      <c r="C12" t="str">
-        <v>LPP tgl 18 mei (koperasi).xls</v>
-      </c>
-      <c r="D12" t="str">
-        <v>LPP tgl 18 mei (koperasi).xls</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
-      </c>
-      <c r="F12" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Total Debit: Rp 79.000 | Total Kredit: Rp 79.000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>8</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-07-25 10:39:01</v>
-      </c>
-      <c r="C13" t="str">
-        <v>LPP tgl 18 mei (loket cabang).xls</v>
-      </c>
-      <c r="D13" t="str">
-        <v>LPP tgl 18 mei (loket cabang).xls</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
-      </c>
-      <c r="F13" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Total Debit: Rp 361.700 | Total Kredit: Rp 361.700</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>9</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-07-25 10:39:01</v>
-      </c>
-      <c r="C14" t="str">
-        <v>LPP tgl 18 mei (loket kantor).xls</v>
-      </c>
-      <c r="D14" t="str">
-        <v>LPP tgl 18 mei (loket kantor).xls</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
-      </c>
-      <c r="F14" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Total Debit: Rp 302.900 | Total Kredit: Rp 302.900</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>10</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-07-25 11:00:17</v>
-      </c>
-      <c r="C15" t="str">
-        <v>AKSESORIES.xls</v>
-      </c>
-      <c r="D15" t="str">
-        <v>AKSESORIES.xls</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
-      </c>
-      <c r="F15" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Total Debit: Rp 21.696.230.000,277 | Total Kredit: Rp 21.696.230.000,277</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>11</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-07-25 11:00:18</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Daftar Voucher.xlsx</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Daftar Voucher.xlsx</v>
-      </c>
-      <c r="E16" t="str">
-        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
-      </c>
-      <c r="F16" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G16" t="str">
-        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>12</v>
-      </c>
-      <c r="B17" t="str">
-        <v>2026-07-25 11:00:18</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Daftar Voucher.xlsx</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Daftar Voucher.xlsx</v>
-      </c>
-      <c r="E17" t="str">
-        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
-      </c>
-      <c r="F17" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>13</v>
-      </c>
-      <c r="B18" t="str">
-        <v>2026-07-25 11:00:18</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Jurnal Bayar.xlsx</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Jurnal Bayar.xlsx</v>
-      </c>
-      <c r="E18" t="str">
-        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
-      </c>
-      <c r="F18" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Total Debit: Rp 200.000 | Total Kredit: Rp 200.000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>14</v>
-      </c>
-      <c r="B19" t="str">
-        <v>2026-07-25 11:00:18</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Jurnal Bayar.xlsx</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Jurnal Bayar.xlsx</v>
-      </c>
-      <c r="E19" t="str">
-        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
-      </c>
-      <c r="F19" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G19" t="str">
-        <v>Total Debit: Rp 125.000 | Total Kredit: Rp 125.000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>15</v>
-      </c>
-      <c r="B20" t="str">
-        <v>2026-07-25 11:00:18</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Persediaan Bahan Kimia &amp; BBM.xlsx</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Persediaan Bahan Kimia &amp; BBM.xlsx</v>
-      </c>
-      <c r="E20" t="str">
-        <v>Persediaan Bahan Kimia &amp; BBM</v>
-      </c>
-      <c r="F20" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Total Debit: Rp 644 | Total Kredit: Rp 644</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>16</v>
-      </c>
-      <c r="B21" t="str">
-        <v>2026-07-25 11:00:18</v>
-      </c>
-      <c r="C21" t="str">
-        <v>LPP tgl 18 mei (koperasi).xls</v>
-      </c>
-      <c r="D21" t="str">
-        <v>LPP tgl 18 mei (koperasi).xls</v>
-      </c>
-      <c r="E21" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
-      </c>
-      <c r="F21" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Total Debit: Rp 79.000 | Total Kredit: Rp 79.000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>17</v>
-      </c>
-      <c r="B22" t="str">
-        <v>2026-07-25 11:00:18</v>
-      </c>
-      <c r="C22" t="str">
-        <v>LPP tgl 18 mei (loket cabang).xls</v>
-      </c>
-      <c r="D22" t="str">
-        <v>LPP tgl 18 mei (loket cabang).xls</v>
-      </c>
-      <c r="E22" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
-      </c>
-      <c r="F22" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Total Debit: Rp 361.700 | Total Kredit: Rp 361.700</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>18</v>
-      </c>
-      <c r="B23" t="str">
-        <v>2026-07-25 11:00:18</v>
-      </c>
-      <c r="C23" t="str">
-        <v>LPP tgl 18 mei (loket kantor).xls</v>
-      </c>
-      <c r="D23" t="str">
-        <v>LPP tgl 18 mei (loket kantor).xls</v>
-      </c>
-      <c r="E23" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
-      </c>
-      <c r="F23" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Total Debit: Rp 302.900 | Total Kredit: Rp 302.900</v>
+      <c r="H5" t="str">
+        <v>SHA-256 Hash Kriptografi</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Hash Sebelumnya (Prev)</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Before State (JSON)</v>
+      </c>
+      <c r="K5" t="str">
+        <v>After State (JSON)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output-app/AUDIT_TRAIL.xlsx
+++ b/output-app/AUDIT_TRAIL.xlsx
@@ -3,7 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="AUDIT LOG" sheetId="1" r:id="rId1"/>
+    <sheet name="Input File Map" sheetId="1" r:id="rId1"/>
+    <sheet name="Journal Entry Audit" sheetId="2" r:id="rId2"/>
+    <sheet name="Output File Map" sheetId="3" r:id="rId3"/>
+    <sheet name="Data Tidak Masuk Output" sheetId="4" r:id="rId4"/>
+    <sheet name="COA Usage" sheetId="5" r:id="rId5"/>
+    <sheet name="Ringkasan" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -32,8 +37,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="10">
+    <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -397,187 +411,2372 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:H12"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="45.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="50.83203125" customWidth="1"/>
-    <col min="8" max="8" width="65.83203125" customWidth="1"/>
-    <col min="9" max="9" width="65.83203125" customWidth="1"/>
-    <col min="10" max="10" width="100.83203125" customWidth="1"/>
-    <col min="11" max="11" width="100.83203125" customWidth="1"/>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="7" max="7" width="35.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>PERUMDAM TIRTA SERUYAN - KABUPATEN SERUYAN</v>
-      </c>
-      <c r="B1" t="str">
-        <v/>
-      </c>
-      <c r="C1" t="str">
-        <v/>
-      </c>
-      <c r="D1" t="str">
-        <v/>
-      </c>
-      <c r="E1" t="str">
-        <v/>
-      </c>
-      <c r="F1" t="str">
-        <v/>
-      </c>
-      <c r="G1" t="str">
-        <v/>
-      </c>
-      <c r="H1" t="str">
-        <v/>
-      </c>
-      <c r="I1" t="str">
-        <v/>
-      </c>
-      <c r="J1" t="str">
-        <v/>
+        <v>AUDIT TRAIL - INPUT FILE MAP LAPORAN KEU</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AUDIT TRAIL (CRYPTOGRAPHIC LOG &amp; DATA SNAPSHOTS)</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Tanggal Cetak: 29/7/2026, 11.53.08</v>
+        <v>No</v>
       </c>
       <c r="B3" t="str">
+        <v>File Input</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Sheet Name</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Baris (Row)</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Kolom (Col)</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Data Diekstrak</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Tujuan (add_tx / Output)</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AKSESORIES.xls</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Sheet0</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Semua baris</v>
+      </c>
+      <c r="E4" t="str">
+        <v>-</v>
+      </c>
+      <c r="F4" t="str">
+        <v>-</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Input ke DB</v>
+      </c>
+      <c r="H4" t="str">
+        <v>TERPROSES</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Daftar Voucher.xlsx</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Sheet0</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Semua baris</v>
+      </c>
+      <c r="E5" t="str">
+        <v>-</v>
+      </c>
+      <c r="F5" t="str">
+        <v>-</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Input ke DB</v>
+      </c>
+      <c r="H5" t="str">
+        <v>TERPROSES</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Jurnal Bayar.xlsx</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Sheet0</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Semua baris</v>
+      </c>
+      <c r="E6" t="str">
+        <v>-</v>
+      </c>
+      <c r="F6" t="str">
+        <v>-</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Input ke DB</v>
+      </c>
+      <c r="H6" t="str">
+        <v>TERPROSES</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>LPP tgl 18 mei (koperasi).xls</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Sheet0</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Semua baris</v>
+      </c>
+      <c r="E7" t="str">
+        <v>-</v>
+      </c>
+      <c r="F7" t="str">
+        <v>-</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Input ke DB</v>
+      </c>
+      <c r="H7" t="str">
+        <v>TERPROSES</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>LPP tgl 18 mei (loket cabang).xls</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Sheet0</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Semua baris</v>
+      </c>
+      <c r="E8" t="str">
+        <v>-</v>
+      </c>
+      <c r="F8" t="str">
+        <v>-</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Input ke DB</v>
+      </c>
+      <c r="H8" t="str">
+        <v>TERPROSES</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>LPP tgl 18 mei (loket kantor).xls</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Sheet0</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Semua baris</v>
+      </c>
+      <c r="E9" t="str">
+        <v>-</v>
+      </c>
+      <c r="F9" t="str">
+        <v>-</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Input ke DB</v>
+      </c>
+      <c r="H9" t="str">
+        <v>TERPROSES</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Persediaan Bahan Kimia &amp; BBM.xlsx</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Sheet0</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Semua baris</v>
+      </c>
+      <c r="E10" t="str">
+        <v>-</v>
+      </c>
+      <c r="F10" t="str">
+        <v>-</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Input ke DB</v>
+      </c>
+      <c r="H10" t="str">
+        <v>TERPROSES</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v/>
       </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>TOTAL FILE INPUT</v>
+      </c>
+      <c r="B12" t="str">
+        <v>7 file</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I12"/>
+  <cols>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="40.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="9" max="9" width="30.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>AUDIT TRAIL - SETIAP BARIS JOURNAL (add_tx)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>No</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Sumber (src)</v>
+      </c>
       <c r="C3" t="str">
+        <v>Ref</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Tgl</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Deskripsi</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Debet</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Credit</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Jumlah (Rp)</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Output yang Terdampak</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AKSESORIES.xls</v>
+      </c>
+      <c r="C4" t="str">
+        <v>AKSESORIES.xls</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
+      </c>
+      <c r="F4" t="str">
+        <v>15.03.00</v>
+      </c>
+      <c r="G4" t="str">
+        <v>71.01.00</v>
+      </c>
+      <c r="H4">
+        <v>21696230000.277</v>
+      </c>
+      <c r="I4" t="str">
+        <v>BUKU BESAR | Journal</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Persediaan Bahan Kimia &amp; BBM.xlsx</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Persediaan Bahan Kimia &amp; BBM.xlsx</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Persediaan Bahan Kimia &amp; BBM</v>
+      </c>
+      <c r="F5" t="str">
+        <v>15.01.00</v>
+      </c>
+      <c r="G5" t="str">
+        <v>71.01.00</v>
+      </c>
+      <c r="H5">
+        <v>644</v>
+      </c>
+      <c r="I5" t="str">
+        <v>BUKU BESAR | Journal</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Daftar Voucher.xlsx</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Daftar Voucher.xlsx</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="F6" t="str">
+        <v>97.06.20</v>
+      </c>
+      <c r="G6" t="str">
+        <v>50.01.00</v>
+      </c>
+      <c r="H6">
+        <v>200000</v>
+      </c>
+      <c r="I6" t="str">
+        <v>BUKU BESAR | Journal</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Jurnal Bayar.xlsx</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Jurnal Bayar.xlsx</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="F7" t="str">
+        <v>50.01.00</v>
+      </c>
+      <c r="G7" t="str">
+        <v>11.01.00</v>
+      </c>
+      <c r="H7">
+        <v>200000</v>
+      </c>
+      <c r="I7" t="str">
+        <v>BUKU BESAR | Journal</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Daftar Voucher.xlsx</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Daftar Voucher.xlsx</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-01-21</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="F8" t="str">
+        <v>15.01.00</v>
+      </c>
+      <c r="G8" t="str">
+        <v>50.01.01</v>
+      </c>
+      <c r="H8">
+        <v>125000</v>
+      </c>
+      <c r="I8" t="str">
+        <v>BUKU BESAR | Journal</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Jurnal Bayar.xlsx</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Jurnal Bayar.xlsx</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-01-21</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="F9" t="str">
+        <v>50.01.00</v>
+      </c>
+      <c r="G9" t="str">
+        <v>11.01.00</v>
+      </c>
+      <c r="H9">
+        <v>125000</v>
+      </c>
+      <c r="I9" t="str">
+        <v>BUKU BESAR | Journal</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="str">
+        <v>LPP tgl 18 mei (koperasi).xls</v>
+      </c>
+      <c r="C10" t="str">
+        <v>LPP tgl 18 mei (koperasi).xls</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="F10" t="str">
+        <v>11.01.00</v>
+      </c>
+      <c r="G10" t="str">
+        <v>13.01.00</v>
+      </c>
+      <c r="H10">
+        <v>79000</v>
+      </c>
+      <c r="I10" t="str">
+        <v>BUKU BESAR | Journal</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str">
+        <v>LPP tgl 18 mei (loket cabang).xls</v>
+      </c>
+      <c r="C11" t="str">
+        <v>LPP tgl 18 mei (loket cabang).xls</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="F11" t="str">
+        <v>11.01.00</v>
+      </c>
+      <c r="G11" t="str">
+        <v>13.01.00</v>
+      </c>
+      <c r="H11">
+        <v>361700</v>
+      </c>
+      <c r="I11" t="str">
+        <v>BUKU BESAR | Journal</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="str">
+        <v>LPP tgl 18 mei (loket kantor).xls</v>
+      </c>
+      <c r="C12" t="str">
+        <v>LPP tgl 18 mei (loket kantor).xls</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="F12" t="str">
+        <v>11.01.00</v>
+      </c>
+      <c r="G12" t="str">
+        <v>13.01.00</v>
+      </c>
+      <c r="H12">
+        <v>302900</v>
+      </c>
+      <c r="I12" t="str">
+        <v>BUKU BESAR | Journal</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G8"/>
+  <cols>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="30.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>AUDIT TRAIL - STRUKTUR FILE OUTPUT</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
         <v/>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>No</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Nama File Output</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Tab Sheet</v>
+      </c>
       <c r="D3" t="str">
+        <v>Cell / Rentang</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Konten</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Data Input Sumber</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Keterangan</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>BUKU BESAR 2026.xlsx</v>
+      </c>
+      <c r="C4" t="str">
+        <v>1 sheet/akun</v>
+      </c>
+      <c r="D4" t="str">
+        <v>A1:F8</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Header + Detail transaksi</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Jurnal DB</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Buku besar per akun</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Journal 2026.xlsx</v>
+      </c>
+      <c r="C5" t="str">
+        <v>JU, DVUD</v>
+      </c>
+      <c r="D5" t="str">
+        <v>A1:K7+</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Header + List jurnal</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Jurnal DB</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Jurnal umum &amp; voucher</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Neraca Lajur 2026.xlsx</v>
+      </c>
+      <c r="C6" t="str">
+        <v>5 sheets (Jan-Mei)</v>
+      </c>
+      <c r="D6" t="str">
+        <v>A1:L7+</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Neraca saldo per bulan</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Jurnal DB</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Neraca lajur bulanan</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Neraca, RL, Arus Kas.xlsx</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Laba-ETAP, Neraca, P-9, P-10</v>
+      </c>
+      <c r="D7" t="str">
+        <v>A1:H30+</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Laporan keuangan</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Jurnal DB</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Laporan finansial</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>AUDIT_TRAIL.xlsx</v>
+      </c>
+      <c r="C8" t="str">
+        <v>6 sheets</v>
+      </c>
+      <c r="D8" t="str">
+        <v>A1:K5+</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Audit trail lengkap</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Semua data</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Input map, jurnal audit, COA usage</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <cols>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="40.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>AUDIT TRAIL - DATA INPUT YANG TIDAK MASUK OUTPUT</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
         <v/>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>No</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Data Input</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Lokasi File/Sheet/Cell</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Alasan Tidak Diproses</v>
+      </c>
       <c r="E3" t="str">
+        <v>Rekomendasi</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Akun tanpa transaksi</v>
+      </c>
+      <c r="C4" t="str">
+        <v>COA Master</v>
+      </c>
+      <c r="D4" t="str">
+        <v>50 akun tidak ada jurnal</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Periksa apakah ada transaksi yang belum diproses</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
         <v/>
       </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G62"/>
+  <cols>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>AUDIT TRAIL - CHART OF ACCOUNTS: MASTER vs PENGGUNAAN</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>No</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Kode Akun</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Nama Akun</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Kategori</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Saldo (Rp)</v>
+      </c>
       <c r="F3" t="str">
+        <v>Digunakan?</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Jml Transaksi</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>11.01.00</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Kas</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E4">
+        <v>418600</v>
+      </c>
+      <c r="F4" t="str">
+        <v>YA</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>11.03.00</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Deposito</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G5" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>13.01.00</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Piutang Usaha</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E6">
+        <v>-381800</v>
+      </c>
+      <c r="F6" t="str">
+        <v>YA</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>13.01.11</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Piutang Rek Air - Tempat Ibadah (TI)</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G7" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>13.01.14</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Piutang Rek Air - Panti Asuhan (PA)</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G8" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>13.01.15</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Piutang Rek Air - Yayasan Sosial (YS)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G9" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="str">
+        <v>13.01.16</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Piutang Rek Air - Sekolah (S)</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G10" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str">
+        <v>13.01.21</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Piutang Rek Air - Rumah Tangga 1 (R1)</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G11" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="str">
+        <v>13.01.22</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Piutang Rek Air - Rumah Tangga 2 (R2)</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G12" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="str">
+        <v>13.01.23</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Piutang Rek Air - Rumah Tangga 3 (R3)</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G13" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="str">
+        <v>13.01.31</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Piutang Rek Air - Niaga Kecil (NK)</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G14" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="str">
+        <v>13.01.32</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Piutang Rek Air - Industri RT</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G15" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="str">
+        <v>13.01.33</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Piutang Rek Air - Inst Pemerintah</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G16" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="str">
+        <v>13.01.35</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Piutang Rek Air - Industri Besar (NB)</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G17" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="str">
+        <v>13.01.36</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Piutang Rek Air - Pelabuhan</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G18" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="str">
+        <v>13.01.40</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Piutang Adm &amp; Dana Meter</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G19" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="str">
+        <v>13.02.00</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Piutang Non Air</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G20" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="str">
+        <v>13.03.00</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Piutang Mitra</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G21" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="str">
+        <v>13.04.00</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Piutang Non Air (Bunga Deposito)</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G22" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="str">
+        <v>14.01.00</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Penyisihan Piutang Usaha</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G23" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="str">
+        <v>15.01.00</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Persediaan Bahan Kimia</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E24">
+        <v>125644</v>
+      </c>
+      <c r="F24" t="str">
+        <v>YA</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="str">
+        <v>15.02.00</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Persediaan BBM (Solar)</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G25" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="str">
+        <v>15.03.00</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Persediaan Bahan Instalasi</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E26">
+        <v>21696230000</v>
+      </c>
+      <c r="F26" t="str">
+        <v>YA</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="str">
+        <v>16.01.00</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Uang Muka Kerja</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Aset Lancar</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G27" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="str">
+        <v>31.01.00</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Aset Tetap</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Aset Tetap</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G28" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="str">
+        <v>32.01.00</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Akumulasi Penyusutan</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Aset Tetap</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G29" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" t="str">
+        <v>33.01.00</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Aset Dalam Penyelesaian</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Aset Tetap</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G30" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="str">
+        <v>50.01.00</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Utang Usaha</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Kewajiban Lancar</v>
+      </c>
+      <c r="E31">
+        <v>-125000</v>
+      </c>
+      <c r="F31" t="str">
+        <v>YA</v>
+      </c>
+      <c r="G31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="str">
+        <v>50.01.01</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Utang Usaha - Bahan Kimia</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Kewajiban Lancar</v>
+      </c>
+      <c r="E32">
+        <v>125000</v>
+      </c>
+      <c r="F32" t="str">
+        <v>YA</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="str">
+        <v>71.01.00</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Kekayaan Pemda Yang Dipisahkan</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Ekuitas</v>
+      </c>
+      <c r="E33">
+        <v>21696230644</v>
+      </c>
+      <c r="F33" t="str">
+        <v>YA</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" t="str">
+        <v>76.01.00</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Laba Ditahan</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Ekuitas</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G34" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35" t="str">
+        <v>77.01.00</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Laba Tahun Berjalan</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Ekuitas</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G35" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36" t="str">
+        <v>81.01.10</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Pendapatan Harga Air</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Pendapatan</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G36" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37" t="str">
+        <v>81.01.20</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Pendapatan Administrasi</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Pendapatan</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G37" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>35</v>
+      </c>
+      <c r="B38" t="str">
+        <v>81.01.30</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Pendapatan Air Mobil Tangki</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Pendapatan</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G38" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39" t="str">
+        <v>81.02.10</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Pendapatan Sambungan Baru</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Pendapatan</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G39" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>37</v>
+      </c>
+      <c r="B40" t="str">
+        <v>81.02.20</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Pendapatan Penyambungan Kembali</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Pendapatan</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G40" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41" t="str">
+        <v>81.02.50</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Pendapatan Denda</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Pendapatan</v>
+      </c>
+      <c r="E41">
+        <v>361800</v>
+      </c>
+      <c r="F41" t="str">
+        <v>YA</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>39</v>
+      </c>
+      <c r="B42" t="str">
+        <v>81.02.60</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Pendapatan Penggantian Meter Rusak</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Pendapatan</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G42" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>40</v>
+      </c>
+      <c r="B43" t="str">
+        <v>81.02.70</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Pendapatan Penggantian Pipa Persil</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Pendapatan</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G43" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44" t="str">
+        <v>81.02.90</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Pendapatan Non Air Lainnya</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Pendapatan</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G44" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45" t="str">
+        <v>91.01.00</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Beban Operasional Sumber Air</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Beban Operasi</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G45" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>43</v>
+      </c>
+      <c r="B46" t="str">
+        <v>92.02.00</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Beban Operasional Pengolahan</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Beban Operasi</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G46" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>44</v>
+      </c>
+      <c r="B47" t="str">
+        <v>92.02.90</v>
+      </c>
+      <c r="C47" t="str">
+        <v>B. Pemeliharaan Pengolahan</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Beban Operasi</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G47" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>45</v>
+      </c>
+      <c r="B48" t="str">
+        <v>93.02.90</v>
+      </c>
+      <c r="C48" t="str">
+        <v>B. Pemeliharaan Trandist Lainnya</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Beban Operasi</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G48" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>46</v>
+      </c>
+      <c r="B49" t="str">
+        <v>96.01.00</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Beban Pegawai</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Beban Umum &amp; Adm</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G49" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>47</v>
+      </c>
+      <c r="B50" t="str">
+        <v>96.02.00</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Beban Kantor</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Beban Umum &amp; Adm</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G50" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>48</v>
+      </c>
+      <c r="B51" t="str">
+        <v>96.02.90</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Rupa-Rupa Beban Kantor</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Beban Umum &amp; Adm</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G51" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>49</v>
+      </c>
+      <c r="B52" t="str">
+        <v>96.03.00</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Beban Hubungan Langganan</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Beban Umum &amp; Adm</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G52" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>50</v>
+      </c>
+      <c r="B53" t="str">
+        <v>96.04.00</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Beban Penelitian &amp; Pengembangan</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Beban Umum &amp; Adm</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G53" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>51</v>
+      </c>
+      <c r="B54" t="str">
+        <v>96.06.00</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Beban Pemeliharaan</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Beban Umum &amp; Adm</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G54" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>52</v>
+      </c>
+      <c r="B55" t="str">
+        <v>96.06.20</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Pemeliharaan Kendaraan</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Beban Umum &amp; Adm</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G55" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>53</v>
+      </c>
+      <c r="B56" t="str">
+        <v>96.06.50</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Beban Pemeliharaan Lainnya</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Beban Umum &amp; Adm</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G56" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>54</v>
+      </c>
+      <c r="B57" t="str">
+        <v>96.07.00</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Biaya Umum Lainnya</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Beban Umum &amp; Adm</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G57" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>55</v>
+      </c>
+      <c r="B58" t="str">
+        <v>96.08.00</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Rupa-Rupa Beban</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Beban Umum &amp; Adm</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G58" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>56</v>
+      </c>
+      <c r="B59" t="str">
+        <v>96.08.80</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Beban Lain-lain</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Beban Umum &amp; Adm</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G59" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>57</v>
+      </c>
+      <c r="B60" t="str">
+        <v>97.01.00</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Beban Pegawai Umum &amp; Adm</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Beban Umum &amp; Adm</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G60" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>58</v>
+      </c>
+      <c r="B61" t="str">
+        <v>97.06.20</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Pemeliharaan Kendaraan</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Beban Umum &amp; Adm</v>
+      </c>
+      <c r="E61">
+        <v>200000</v>
+      </c>
+      <c r="F61" t="str">
+        <v>YA</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>59</v>
+      </c>
+      <c r="B62" t="str">
+        <v>98.08.80</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Beban Lain-lain</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Beban Umum &amp; Adm</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62" t="str">
+        <v>TIDAK</v>
+      </c>
+      <c r="G62" t="str">
+        <v>-</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B12"/>
+  <cols>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="50.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>RINGKASAN AUDIT TRAIL</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
         <v/>
       </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v/>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TANGGAL GENERATE</v>
+      </c>
+      <c r="B3" t="str">
+        <v>30 Jul 2026 10.53.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v/>
+        <v>ENTITY</v>
       </c>
       <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v/>
+        <v>PERUSAHAAN DAERAH AIR MINUM KABUPATEN SERUYAN</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>No</v>
+        <v>TOTAL INPUT FILE DIPROSES</v>
       </c>
       <c r="B5" t="str">
-        <v>Waktu / Timestamp</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Kategori / Sumber</v>
-      </c>
-      <c r="D5" t="str">
-        <v>File Input / Ref</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Deskripsi Operasi</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Status</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Detail Mutasi / Ringkasan</v>
-      </c>
-      <c r="H5" t="str">
-        <v>SHA-256 Hash Kriptografi</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Hash Sebelumnya (Prev)</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Before State (JSON)</v>
-      </c>
-      <c r="K5" t="str">
-        <v>After State (JSON)</v>
+        <v>7 file</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TOTAL TRANSAKSI (add_tx)</v>
+      </c>
+      <c r="B6" t="str">
+        <v>9 transaksi</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>TOTAL JURNAL ENTRIES</v>
+      </c>
+      <c r="B7" t="str">
+        <v>21 entries</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>TOTAL AKUN BUKU BESAR</v>
+      </c>
+      <c r="B8" t="str">
+        <v>9 dari 59 di COA</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>TOTAL AKUN DIGUNAKAN</v>
+      </c>
+      <c r="B9" t="str">
+        <v>9 dari 59 akun</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>TOTAL AKUN TIDAK DIGUNAKAN</v>
+      </c>
+      <c r="B10" t="str">
+        <v>50 akun</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>STATUS PROSES</v>
+      </c>
+      <c r="B12" t="str">
+        <v>SEMUA PROSES BERHASIL</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output-app/AUDIT_TRAIL.xlsx
+++ b/output-app/AUDIT_TRAIL.xlsx
@@ -478,7 +478,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Tanggal Cetak: 29/7/2026, 11.53.08</v>
+        <v>Tanggal Cetak: 29/7/2026, 13.32.54</v>
       </c>
       <c r="B3" t="str">
         <v/>
